--- a/snareseq2/v2.0.0/snareseq2-v2.0.0.xlsx
+++ b/snareseq2/v2.0.0/snareseq2-v2.0.0.xlsx
@@ -22,6 +22,11 @@
   <commentList>
     <comment ref="A1" authorId="1">
       <text>
+        <t>A styled paragraph describing the assay</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1">
+      <text>
         <t>(Required) The unique identifier from HuBMAP or SenNet for the sample (such as a
 block, section, or suspension) used to perform the assay. For instance, in an
 RNAseq assay, the parent sample would be the suspension, while in imaging
@@ -30,15 +35,15 @@
 Example: HBM386.ZGKG.235, HBM672.MKPK.442</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="1">
+    <comment ref="C1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="1">
+    <comment ref="D1" authorId="1">
       <text>
         <t>(Required) The DOI for the protocols.io page that details the assay or the
 procedures used for sample procurement and preparation. For example, in the case
@@ -48,18 +53,18 @@
 Example: https://dx.doi.org/10.17504/protocols.io.eq2lyno9qvx9/v1</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="E1" authorId="1">
       <text>
         <t>(Required) The specific type of dataset being produced. Example: RNAseq</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="F1" authorId="1">
       <text>
         <t>(Required) The name of the file containing the ORCID IDs for all contributors to
 this dataset. Example: ./contributors.csv</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="G1" authorId="1">
       <text>
         <t>(Required) The top-level directory containing the raw and/or processed data. For
 a single dataset upload, this might be represented as ".", whereas for a data
@@ -71,13 +76,13 @@
 an internal metadata field used solely for data ingestion. Example: ./TEST001-RK</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <t>The number of PCR cycles performed following the Chromium Controller step and
 before the suspension is separated and library construction begins. Example: 7</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <t>(Required) The unique string identifier for the metadata specification version,
 which is easily interpretable by computers for purposes of data validation and
@@ -89,7 +94,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
+  <si>
+    <t>assay_description</t>
+  </si>
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -103,304 +111,364 @@
     <t>dataset_type</t>
   </si>
   <si>
+    <t>Cell DIVE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
+  </si>
+  <si>
+    <t>Light Sheet</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+  </si>
+  <si>
+    <t>MIBI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
+  </si>
+  <si>
     <t>HiFi-Slide</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000195</t>
   </si>
   <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
+  </si>
+  <si>
+    <t>PhenoCycler</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
+  </si>
+  <si>
+    <t>CyCIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
+  </si>
+  <si>
+    <t>MALDI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
+  </si>
+  <si>
+    <t>SIMS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
+  </si>
+  <si>
+    <t>DESI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
+  </si>
+  <si>
+    <t>Auto-fluorescence</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
+  </si>
+  <si>
+    <t>Confocal</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
+  </si>
+  <si>
+    <t>Thick section Multiphoton MxIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
+  </si>
+  <si>
+    <t>Second Harmonic Generation (SHG)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
+  </si>
+  <si>
+    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
+  </si>
+  <si>
+    <t>10X Multiome</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
+  </si>
+  <si>
+    <t>Molecular Cartography</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
+  </si>
+  <si>
+    <t>CosMx Transcriptomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
+  </si>
+  <si>
+    <t>Xenium</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+  </si>
+  <si>
+    <t>MERFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
+  </si>
+  <si>
     <t>SNARE-seq2</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000264</t>
   </si>
   <si>
+    <t>2D Imaging Mass Cytometry</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
+  </si>
+  <si>
+    <t>GeoMx (NGS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
+  </si>
+  <si>
+    <t>GeoMx (nCounter)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
+  </si>
+  <si>
+    <t>Visium (no probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
+  </si>
+  <si>
+    <t>Visium (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
+  </si>
+  <si>
+    <t>ATACseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
+  </si>
+  <si>
+    <t>RNAseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
+  </si>
+  <si>
+    <t>RNAseq (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
+  </si>
+  <si>
+    <t>nanoSPLITS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
+  </si>
+  <si>
+    <t>Resolve</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
+  </si>
+  <si>
+    <t>Stereo-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
+  </si>
+  <si>
+    <t>Seq-Scope</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
+  </si>
+  <si>
+    <t>DART-FISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
+  </si>
+  <si>
+    <t>seqFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
+  </si>
+  <si>
+    <t>MS Lipidomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
+  </si>
+  <si>
+    <t>CyTOF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
+  </si>
+  <si>
+    <t>DBiT-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
+  </si>
+  <si>
+    <t>Singular Genomics G4X</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
+  </si>
+  <si>
+    <t>CosMx Proteomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
+  </si>
+  <si>
+    <t>FACS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
+  </si>
+  <si>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
+  </si>
+  <si>
+    <t>4i</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
+  </si>
+  <si>
+    <t>MPLEx</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+  </si>
+  <si>
+    <t>Pixel-seqV2</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
+  </si>
+  <si>
+    <t>Visium HD</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
+  </si>
+  <si>
     <t>COMET</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000458</t>
   </si>
   <si>
-    <t>Visium (no probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
-  </si>
-  <si>
-    <t>DESI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
-  </si>
-  <si>
-    <t>Confocal</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
-  </si>
-  <si>
-    <t>Stereo-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
-  </si>
-  <si>
-    <t>Visium (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
-  </si>
-  <si>
-    <t>Molecular Cartography</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
-  </si>
-  <si>
-    <t>DBiT-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
-  </si>
-  <si>
-    <t>Seq-Scope</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
-  </si>
-  <si>
-    <t>CosMx Transcriptomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
-  </si>
-  <si>
-    <t>CyCIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
-  </si>
-  <si>
-    <t>Light Sheet</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
-  </si>
-  <si>
-    <t>seqFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
-  </si>
-  <si>
-    <t>ATACseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
-  </si>
-  <si>
-    <t>CosMx Proteomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
-  </si>
-  <si>
-    <t>Singular Genomics G4X</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
-  </si>
-  <si>
-    <t>Visium HD</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
-  </si>
-  <si>
-    <t>MERFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
-  </si>
-  <si>
-    <t>10X Multiome</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
-  </si>
-  <si>
-    <t>4i</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
-  </si>
-  <si>
-    <t>PhenoCycler</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
-  </si>
-  <si>
-    <t>Second Harmonic Generation (SHG)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
-  </si>
-  <si>
-    <t>Thick section Multiphoton MxIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
-  </si>
-  <si>
-    <t>CyTOF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
-  </si>
-  <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
-  </si>
-  <si>
-    <t>MIBI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
-  </si>
-  <si>
-    <t>Auto-fluorescence</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
-  </si>
-  <si>
-    <t>FACS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
-  </si>
-  <si>
-    <t>Xenium</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
-  </si>
-  <si>
-    <t>SIMS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
-  </si>
-  <si>
-    <t>Cell DIVE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
-  </si>
-  <si>
-    <t>CODEX</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
-  </si>
-  <si>
-    <t>GeoMx (NGS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
-  </si>
-  <si>
-    <t>Pixel-seqV2</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
-  </si>
-  <si>
-    <t>MALDI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
-  </si>
-  <si>
-    <t>2D Imaging Mass Cytometry</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
-  </si>
-  <si>
-    <t>Histology</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
-  </si>
-  <si>
-    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
-  </si>
-  <si>
-    <t>DART-FISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
-  </si>
-  <si>
-    <t>Resolve</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
-  </si>
-  <si>
-    <t>RNAseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
-  </si>
-  <si>
-    <t>nanoSPLITS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
-  </si>
-  <si>
-    <t>GeoMx (nCounter)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
-  </si>
-  <si>
-    <t>RNAseq (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
-  </si>
-  <si>
-    <t>MS Lipidomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
-  </si>
-  <si>
-    <t>MPLEx</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+    <t>Virtual Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000473</t>
+  </si>
+  <si>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
+  </si>
+  <si>
+    <t>iCLAP</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
+  </si>
+  <si>
+    <t>MACSima</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
+  </si>
+  <si>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
+    <t>snm3C-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000504</t>
+  </si>
+  <si>
+    <t>Whole Exome Sequencing</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000514</t>
   </si>
   <si>
     <t>contributors_path</t>
@@ -433,7 +501,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2025-10-21T13:32:46-07:00</t>
+    <t>2026-10-21T13:36:32-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -492,11 +560,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -515,17 +584,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" style="2" width="14.39453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" style="3" width="5.46875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" style="4" width="20.234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" style="5" width="10.59765625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" style="6" width="14.5859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" style="7" width="8.46484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" style="8" width="31.91796875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" style="9" width="16.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" style="2" width="14.46875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" style="3" width="14.39453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" style="4" width="5.46875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" style="5" width="20.234375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" style="6" width="10.59765625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" style="7" width="14.5859375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" style="8" width="8.46484375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" style="9" width="31.91796875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" style="10" width="16.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,32 +612,35 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>107</v>
+        <v>127</v>
+      </c>
+      <c r="I1" t="s" s="1">
+        <v>128</v>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="s" s="5">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s" s="9">
-        <v>108</v>
+      <c r="E2" t="s" s="6">
+        <v>49</v>
+      </c>
+      <c r="I2" t="s" s="10">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$50</formula1>
+    <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'dataset_type'!$A$1:$A$60</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
@@ -580,407 +653,487 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1001,30 +1154,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
